--- a/output/pdf_financials_xlsx/SRV.UN.xlsx
+++ b/output/pdf_financials_xlsx/SRV.UN.xlsx
@@ -1126,36 +1126,32 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -2215,25 +2211,25 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-15.034896</v>
+        <v>-18.034896</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>7.657737</v>
+        <v>4.657737</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>8.042959</v>
+        <v>5.042959</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>9.897893</v>
+        <v>6.897893</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11.181938</v>
+        <v>8.181938000000001</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>12.328573</v>
+        <v>9.328573</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>13.612136</v>
+        <v>10.612136</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>7.546704</v>
@@ -2335,25 +2331,25 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-15.034896</v>
+        <v>-18.034896</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>7.657737</v>
+        <v>4.657737</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>8.042959</v>
+        <v>5.042959</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.897893</v>
+        <v>6.897893</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>11.181938</v>
+        <v>8.181938000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>12.328573</v>
+        <v>9.328573</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>13.612136</v>
+        <v>10.612136</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>7.546704</v>
@@ -2646,49 +2642,49 @@
         <v>9.6e-05</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.100464</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.316588</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.577089</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.478655</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.340896</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.373651</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.296246</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.136944</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.138629</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.41313</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.27532</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.412181</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.044762</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.320614</v>
       </c>
     </row>
     <row r="35">
@@ -2762,49 +2758,49 @@
         <v>9.6e-05</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.100464</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.316588</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.577089</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.478655</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.340896</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.373651</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.296246</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.136944</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.138629</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.41313</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.27532</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.412181</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.044762</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.320614</v>
       </c>
     </row>
     <row r="37">
@@ -3458,49 +3454,49 @@
         <v>1.21671</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.216806</v>
+        <v>1.21671</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.314058</v>
+        <v>1.213594</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.457655</v>
+        <v>1.141067</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.638741</v>
+        <v>1.061652</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.483869</v>
+        <v>1.005214</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.08497</v>
+        <v>3.744074</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>4.332796</v>
+        <v>3.959145</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.494323</v>
+        <v>4.198077</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>4.331429</v>
+        <v>4.194485</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.885998</v>
+        <v>4.747369</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.872358</v>
+        <v>4.459228</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>5.486601</v>
+        <v>3.211281</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>3.97319</v>
+        <v>3.561009</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>4.779232</v>
+        <v>3.73447</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>3.580056</v>
+        <v>3.259442</v>
       </c>
     </row>
     <row r="49">
@@ -9035,7 +9031,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10620,7 +10616,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -24493,7 +24489,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -25592,7 +25588,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -28148,7 +28144,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -30162,7 +30158,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -31265,7 +31261,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E232" s="5" t="n">

--- a/output/pdf_financials_xlsx/SRV.UN.xlsx
+++ b/output/pdf_financials_xlsx/SRV.UN.xlsx
@@ -17057,7 +17057,11 @@
           <t>Recovery of future income taxes (note 11)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -17457,7 +17461,11 @@
           <t>Recovery of future income taxes (note 12)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
